--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Histórico" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Histórico" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$223</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4751,8 +4751,859 @@
         </is>
       </c>
     </row>
+    <row r="187" ht="42" customHeight="1">
+      <c r="A187" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="42" customHeight="1">
+      <c r="A188" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="42" customHeight="1">
+      <c r="A189" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="42" customHeight="1">
+      <c r="A190" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="42" customHeight="1">
+      <c r="A191" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="42" customHeight="1">
+      <c r="A192" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="42" customHeight="1">
+      <c r="A193" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="42" customHeight="1">
+      <c r="A194" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="42" customHeight="1">
+      <c r="A195" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="42" customHeight="1">
+      <c r="A196" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="42" customHeight="1">
+      <c r="A197" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="42" customHeight="1">
+      <c r="A198" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="42" customHeight="1">
+      <c r="A199" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="42" customHeight="1">
+      <c r="A200" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="42" customHeight="1">
+      <c r="A201" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="42" customHeight="1">
+      <c r="A202" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="42" customHeight="1">
+      <c r="A203" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="42" customHeight="1">
+      <c r="A204" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="42" customHeight="1">
+      <c r="A205" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="42" customHeight="1">
+      <c r="A206" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="42" customHeight="1">
+      <c r="A207" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="42" customHeight="1">
+      <c r="A208" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="42" customHeight="1">
+      <c r="A209" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="42" customHeight="1">
+      <c r="A210" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="42" customHeight="1">
+      <c r="A211" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="42" customHeight="1">
+      <c r="A212" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="42" customHeight="1">
+      <c r="A213" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="42" customHeight="1">
+      <c r="A214" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="42" customHeight="1">
+      <c r="A215" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="42" customHeight="1">
+      <c r="A216" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="42" customHeight="1">
+      <c r="A217" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="42" customHeight="1">
+      <c r="A218" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="42" customHeight="1">
+      <c r="A219" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="42" customHeight="1">
+      <c r="A220" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="42" customHeight="1">
+      <c r="A221" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="42" customHeight="1">
+      <c r="A222" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="42" customHeight="1">
+      <c r="A223" s="5" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E186"/>
+  <autoFilter ref="A1:E223"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Histórico" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Histórico" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$260</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5602,8 +5602,859 @@
         </is>
       </c>
     </row>
+    <row r="224" ht="42" customHeight="1">
+      <c r="A224" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="42" customHeight="1">
+      <c r="A225" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="42" customHeight="1">
+      <c r="A226" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="42" customHeight="1">
+      <c r="A227" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="42" customHeight="1">
+      <c r="A228" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="42" customHeight="1">
+      <c r="A229" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="42" customHeight="1">
+      <c r="A230" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="42" customHeight="1">
+      <c r="A231" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="42" customHeight="1">
+      <c r="A232" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="42" customHeight="1">
+      <c r="A233" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="42" customHeight="1">
+      <c r="A234" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="42" customHeight="1">
+      <c r="A235" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="42" customHeight="1">
+      <c r="A236" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="42" customHeight="1">
+      <c r="A237" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="42" customHeight="1">
+      <c r="A238" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="42" customHeight="1">
+      <c r="A239" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="42" customHeight="1">
+      <c r="A240" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="42" customHeight="1">
+      <c r="A241" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="42" customHeight="1">
+      <c r="A242" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="42" customHeight="1">
+      <c r="A243" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="42" customHeight="1">
+      <c r="A244" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="42" customHeight="1">
+      <c r="A245" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="42" customHeight="1">
+      <c r="A246" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="42" customHeight="1">
+      <c r="A247" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="42" customHeight="1">
+      <c r="A248" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="42" customHeight="1">
+      <c r="A249" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="42" customHeight="1">
+      <c r="A250" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="42" customHeight="1">
+      <c r="A251" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="42" customHeight="1">
+      <c r="A252" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="42" customHeight="1">
+      <c r="A253" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="42" customHeight="1">
+      <c r="A254" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="42" customHeight="1">
+      <c r="A255" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="42" customHeight="1">
+      <c r="A256" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="42" customHeight="1">
+      <c r="A257" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="42" customHeight="1">
+      <c r="A258" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="42" customHeight="1">
+      <c r="A259" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="42" customHeight="1">
+      <c r="A260" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E223"/>
+  <autoFilter ref="A1:E260"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$334</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6453,8 +6453,1710 @@
         </is>
       </c>
     </row>
+    <row r="261" ht="42" customHeight="1">
+      <c r="A261" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="42" customHeight="1">
+      <c r="A262" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="42" customHeight="1">
+      <c r="A263" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="42" customHeight="1">
+      <c r="A264" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="42" customHeight="1">
+      <c r="A265" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="42" customHeight="1">
+      <c r="A266" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="42" customHeight="1">
+      <c r="A267" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="42" customHeight="1">
+      <c r="A268" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="42" customHeight="1">
+      <c r="A269" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="42" customHeight="1">
+      <c r="A270" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="42" customHeight="1">
+      <c r="A271" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="42" customHeight="1">
+      <c r="A272" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="42" customHeight="1">
+      <c r="A273" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="42" customHeight="1">
+      <c r="A274" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="42" customHeight="1">
+      <c r="A275" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="42" customHeight="1">
+      <c r="A276" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="42" customHeight="1">
+      <c r="A277" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="42" customHeight="1">
+      <c r="A278" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="42" customHeight="1">
+      <c r="A279" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="42" customHeight="1">
+      <c r="A280" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="42" customHeight="1">
+      <c r="A281" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="42" customHeight="1">
+      <c r="A282" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="42" customHeight="1">
+      <c r="A283" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="42" customHeight="1">
+      <c r="A284" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="42" customHeight="1">
+      <c r="A285" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="42" customHeight="1">
+      <c r="A286" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="42" customHeight="1">
+      <c r="A287" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="42" customHeight="1">
+      <c r="A288" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="42" customHeight="1">
+      <c r="A289" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="42" customHeight="1">
+      <c r="A290" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="42" customHeight="1">
+      <c r="A291" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="42" customHeight="1">
+      <c r="A292" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="42" customHeight="1">
+      <c r="A293" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="42" customHeight="1">
+      <c r="A294" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="42" customHeight="1">
+      <c r="A295" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="42" customHeight="1">
+      <c r="A296" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="42" customHeight="1">
+      <c r="A297" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="42" customHeight="1">
+      <c r="A298" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="42" customHeight="1">
+      <c r="A299" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="42" customHeight="1">
+      <c r="A300" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="42" customHeight="1">
+      <c r="A301" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="42" customHeight="1">
+      <c r="A302" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="42" customHeight="1">
+      <c r="A303" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="42" customHeight="1">
+      <c r="A304" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="42" customHeight="1">
+      <c r="A305" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="42" customHeight="1">
+      <c r="A306" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="42" customHeight="1">
+      <c r="A307" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="42" customHeight="1">
+      <c r="A308" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="42" customHeight="1">
+      <c r="A309" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="42" customHeight="1">
+      <c r="A310" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="42" customHeight="1">
+      <c r="A311" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="42" customHeight="1">
+      <c r="A312" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="42" customHeight="1">
+      <c r="A313" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="42" customHeight="1">
+      <c r="A314" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="42" customHeight="1">
+      <c r="A315" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="42" customHeight="1">
+      <c r="A316" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="42" customHeight="1">
+      <c r="A317" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="42" customHeight="1">
+      <c r="A318" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="42" customHeight="1">
+      <c r="A319" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="42" customHeight="1">
+      <c r="A320" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="42" customHeight="1">
+      <c r="A321" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="42" customHeight="1">
+      <c r="A322" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="42" customHeight="1">
+      <c r="A323" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="42" customHeight="1">
+      <c r="A324" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="42" customHeight="1">
+      <c r="A325" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="42" customHeight="1">
+      <c r="A326" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="42" customHeight="1">
+      <c r="A327" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="42" customHeight="1">
+      <c r="A328" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="42" customHeight="1">
+      <c r="A329" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="42" customHeight="1">
+      <c r="A330" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="42" customHeight="1">
+      <c r="A331" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="42" customHeight="1">
+      <c r="A332" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="42" customHeight="1">
+      <c r="A333" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="42" customHeight="1">
+      <c r="A334" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E260"/>
+  <autoFilter ref="A1:E334"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$408</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E334"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8155,8 +8155,1710 @@
         </is>
       </c>
     </row>
+    <row r="335" ht="42" customHeight="1">
+      <c r="A335" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="42" customHeight="1">
+      <c r="A336" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="42" customHeight="1">
+      <c r="A337" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="42" customHeight="1">
+      <c r="A338" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="42" customHeight="1">
+      <c r="A339" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="42" customHeight="1">
+      <c r="A340" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="42" customHeight="1">
+      <c r="A341" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="42" customHeight="1">
+      <c r="A342" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="42" customHeight="1">
+      <c r="A343" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="42" customHeight="1">
+      <c r="A344" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="42" customHeight="1">
+      <c r="A345" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="42" customHeight="1">
+      <c r="A346" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="42" customHeight="1">
+      <c r="A347" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="42" customHeight="1">
+      <c r="A348" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="42" customHeight="1">
+      <c r="A349" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="42" customHeight="1">
+      <c r="A350" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="42" customHeight="1">
+      <c r="A351" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="42" customHeight="1">
+      <c r="A352" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E352" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="42" customHeight="1">
+      <c r="A353" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E353" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="42" customHeight="1">
+      <c r="A354" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E354" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="42" customHeight="1">
+      <c r="A355" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E355" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="42" customHeight="1">
+      <c r="A356" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E356" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="42" customHeight="1">
+      <c r="A357" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C357" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E357" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="42" customHeight="1">
+      <c r="A358" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E358" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="42" customHeight="1">
+      <c r="A359" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E359" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="42" customHeight="1">
+      <c r="A360" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="42" customHeight="1">
+      <c r="A361" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E361" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="42" customHeight="1">
+      <c r="A362" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="42" customHeight="1">
+      <c r="A363" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D363" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="42" customHeight="1">
+      <c r="A364" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="42" customHeight="1">
+      <c r="A365" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="42" customHeight="1">
+      <c r="A366" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="42" customHeight="1">
+      <c r="A367" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E367" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="42" customHeight="1">
+      <c r="A368" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E368" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="42" customHeight="1">
+      <c r="A369" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D369" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E369" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="42" customHeight="1">
+      <c r="A370" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D370" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E370" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="42" customHeight="1">
+      <c r="A371" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C371" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E371" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="42" customHeight="1">
+      <c r="A372" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C372" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E372" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="42" customHeight="1">
+      <c r="A373" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C373" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E373" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="42" customHeight="1">
+      <c r="A374" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C374" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D374" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="42" customHeight="1">
+      <c r="A375" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D375" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E375" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="42" customHeight="1">
+      <c r="A376" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D376" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E376" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="42" customHeight="1">
+      <c r="A377" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C377" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D377" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E377" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="42" customHeight="1">
+      <c r="A378" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C378" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D378" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E378" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="42" customHeight="1">
+      <c r="A379" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E379" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="42" customHeight="1">
+      <c r="A380" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C380" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E380" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="42" customHeight="1">
+      <c r="A381" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C381" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E381" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="42" customHeight="1">
+      <c r="A382" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C382" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D382" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E382" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="42" customHeight="1">
+      <c r="A383" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E383" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="42" customHeight="1">
+      <c r="A384" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="42" customHeight="1">
+      <c r="A385" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C385" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="42" customHeight="1">
+      <c r="A386" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C386" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="42" customHeight="1">
+      <c r="A387" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E387" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="42" customHeight="1">
+      <c r="A388" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C388" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="42" customHeight="1">
+      <c r="A389" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C389" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E389" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="42" customHeight="1">
+      <c r="A390" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C390" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D390" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E390" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="42" customHeight="1">
+      <c r="A391" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B391" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C391" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="42" customHeight="1">
+      <c r="A392" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C392" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D392" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="42" customHeight="1">
+      <c r="A393" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C393" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D393" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E393" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="42" customHeight="1">
+      <c r="A394" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C394" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D394" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E394" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="42" customHeight="1">
+      <c r="A395" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C395" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="42" customHeight="1">
+      <c r="A396" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C396" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D396" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E396" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="42" customHeight="1">
+      <c r="A397" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C397" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D397" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E397" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="42" customHeight="1">
+      <c r="A398" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C398" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D398" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E398" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="42" customHeight="1">
+      <c r="A399" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C399" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="42" customHeight="1">
+      <c r="A400" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C400" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D400" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="42" customHeight="1">
+      <c r="A401" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C401" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="42" customHeight="1">
+      <c r="A402" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C402" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="42" customHeight="1">
+      <c r="A403" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D403" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="42" customHeight="1">
+      <c r="A404" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C404" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D404" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="42" customHeight="1">
+      <c r="A405" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C405" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D405" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E405" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="42" customHeight="1">
+      <c r="A406" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C406" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D406" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E406" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="42" customHeight="1">
+      <c r="A407" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C407" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D407" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E407" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="42" customHeight="1">
+      <c r="A408" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C408" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D408" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E408" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E334"/>
+  <autoFilter ref="A1:E408"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$408</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$445</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E408"/>
+  <dimension ref="A1:E445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9857,8 +9857,859 @@
         </is>
       </c>
     </row>
+    <row r="409" ht="42" customHeight="1">
+      <c r="A409" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C409" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D409" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="42" customHeight="1">
+      <c r="A410" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C410" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D410" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E410" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="42" customHeight="1">
+      <c r="A411" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C411" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D411" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E411" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="42" customHeight="1">
+      <c r="A412" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C412" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D412" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="42" customHeight="1">
+      <c r="A413" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B413" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D413" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E413" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="42" customHeight="1">
+      <c r="A414" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C414" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D414" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E414" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="42" customHeight="1">
+      <c r="A415" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C415" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D415" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E415" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="42" customHeight="1">
+      <c r="A416" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C416" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D416" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E416" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="42" customHeight="1">
+      <c r="A417" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B417" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C417" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D417" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E417" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="42" customHeight="1">
+      <c r="A418" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C418" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D418" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E418" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="42" customHeight="1">
+      <c r="A419" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B419" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C419" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D419" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E419" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="42" customHeight="1">
+      <c r="A420" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C420" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D420" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E420" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="42" customHeight="1">
+      <c r="A421" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B421" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C421" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D421" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E421" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="42" customHeight="1">
+      <c r="A422" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C422" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D422" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E422" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="42" customHeight="1">
+      <c r="A423" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B423" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C423" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D423" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E423" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="42" customHeight="1">
+      <c r="A424" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C424" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E424" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="42" customHeight="1">
+      <c r="A425" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C425" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D425" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E425" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="42" customHeight="1">
+      <c r="A426" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C426" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D426" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E426" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="42" customHeight="1">
+      <c r="A427" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C427" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D427" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E427" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="42" customHeight="1">
+      <c r="A428" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C428" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E428" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="42" customHeight="1">
+      <c r="A429" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B429" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C429" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D429" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E429" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="42" customHeight="1">
+      <c r="A430" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C430" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D430" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E430" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="42" customHeight="1">
+      <c r="A431" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B431" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C431" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D431" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E431" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="42" customHeight="1">
+      <c r="A432" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C432" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D432" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E432" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="42" customHeight="1">
+      <c r="A433" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C433" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D433" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E433" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="42" customHeight="1">
+      <c r="A434" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D434" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E434" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="42" customHeight="1">
+      <c r="A435" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D435" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E435" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="42" customHeight="1">
+      <c r="A436" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C436" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E436" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="42" customHeight="1">
+      <c r="A437" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B437" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C437" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D437" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E437" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="42" customHeight="1">
+      <c r="A438" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C438" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E438" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="42" customHeight="1">
+      <c r="A439" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B439" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C439" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D439" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E439" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="42" customHeight="1">
+      <c r="A440" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C440" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D440" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E440" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="42" customHeight="1">
+      <c r="A441" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C441" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E441" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="42" customHeight="1">
+      <c r="A442" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C442" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D442" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E442" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="42" customHeight="1">
+      <c r="A443" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B443" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C443" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D443" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E443" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="42" customHeight="1">
+      <c r="A444" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C444" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D444" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E444" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="42" customHeight="1">
+      <c r="A445" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B445" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C445" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D445" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E445" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E408"/>
+  <autoFilter ref="A1:E445"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$445</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$519</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E445"/>
+  <dimension ref="A1:E519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10708,8 +10708,1710 @@
         </is>
       </c>
     </row>
+    <row r="446" ht="42" customHeight="1">
+      <c r="A446" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C446" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D446" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E446" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="42" customHeight="1">
+      <c r="A447" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B447" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C447" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D447" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E447" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="42" customHeight="1">
+      <c r="A448" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C448" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D448" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E448" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="42" customHeight="1">
+      <c r="A449" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B449" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C449" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D449" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E449" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="42" customHeight="1">
+      <c r="A450" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C450" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D450" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E450" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="42" customHeight="1">
+      <c r="A451" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B451" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C451" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D451" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E451" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="42" customHeight="1">
+      <c r="A452" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C452" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D452" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E452" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="42" customHeight="1">
+      <c r="A453" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B453" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C453" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D453" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E453" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="42" customHeight="1">
+      <c r="A454" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C454" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D454" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E454" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="42" customHeight="1">
+      <c r="A455" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B455" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C455" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D455" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E455" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="42" customHeight="1">
+      <c r="A456" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C456" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D456" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E456" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="42" customHeight="1">
+      <c r="A457" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B457" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C457" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D457" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E457" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="42" customHeight="1">
+      <c r="A458" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C458" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D458" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E458" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="42" customHeight="1">
+      <c r="A459" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B459" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C459" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D459" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E459" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="42" customHeight="1">
+      <c r="A460" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C460" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D460" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E460" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="42" customHeight="1">
+      <c r="A461" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B461" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C461" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D461" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E461" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="42" customHeight="1">
+      <c r="A462" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C462" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D462" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E462" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="42" customHeight="1">
+      <c r="A463" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B463" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C463" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D463" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E463" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="42" customHeight="1">
+      <c r="A464" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C464" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D464" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E464" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="42" customHeight="1">
+      <c r="A465" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B465" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C465" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D465" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E465" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="42" customHeight="1">
+      <c r="A466" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C466" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D466" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E466" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="42" customHeight="1">
+      <c r="A467" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B467" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C467" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D467" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E467" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="42" customHeight="1">
+      <c r="A468" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C468" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D468" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E468" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="42" customHeight="1">
+      <c r="A469" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C469" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D469" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E469" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="42" customHeight="1">
+      <c r="A470" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C470" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D470" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E470" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="42" customHeight="1">
+      <c r="A471" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C471" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D471" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E471" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="42" customHeight="1">
+      <c r="A472" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C472" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D472" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E472" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="42" customHeight="1">
+      <c r="A473" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B473" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C473" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D473" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E473" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="42" customHeight="1">
+      <c r="A474" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C474" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D474" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E474" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="42" customHeight="1">
+      <c r="A475" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B475" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C475" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D475" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E475" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="42" customHeight="1">
+      <c r="A476" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C476" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D476" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E476" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="42" customHeight="1">
+      <c r="A477" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B477" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C477" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D477" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E477" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="42" customHeight="1">
+      <c r="A478" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C478" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D478" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E478" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="42" customHeight="1">
+      <c r="A479" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B479" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C479" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D479" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E479" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="42" customHeight="1">
+      <c r="A480" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C480" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D480" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E480" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="42" customHeight="1">
+      <c r="A481" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C481" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D481" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E481" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="42" customHeight="1">
+      <c r="A482" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C482" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D482" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E482" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="42" customHeight="1">
+      <c r="A483" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C483" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D483" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="42" customHeight="1">
+      <c r="A484" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C484" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D484" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="42" customHeight="1">
+      <c r="A485" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B485" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C485" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D485" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E485" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="42" customHeight="1">
+      <c r="A486" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C486" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D486" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E486" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="42" customHeight="1">
+      <c r="A487" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C487" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D487" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E487" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="42" customHeight="1">
+      <c r="A488" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C488" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D488" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E488" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="42" customHeight="1">
+      <c r="A489" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B489" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C489" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D489" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E489" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="42" customHeight="1">
+      <c r="A490" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C490" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D490" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E490" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="42" customHeight="1">
+      <c r="A491" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B491" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C491" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D491" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E491" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="42" customHeight="1">
+      <c r="A492" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C492" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D492" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E492" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="42" customHeight="1">
+      <c r="A493" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C493" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D493" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E493" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="42" customHeight="1">
+      <c r="A494" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C494" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D494" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E494" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="42" customHeight="1">
+      <c r="A495" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C495" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D495" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E495" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="42" customHeight="1">
+      <c r="A496" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C496" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D496" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E496" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="42" customHeight="1">
+      <c r="A497" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C497" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D497" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E497" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="42" customHeight="1">
+      <c r="A498" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C498" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D498" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E498" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="42" customHeight="1">
+      <c r="A499" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B499" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C499" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D499" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E499" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="42" customHeight="1">
+      <c r="A500" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B500" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C500" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D500" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E500" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="42" customHeight="1">
+      <c r="A501" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B501" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C501" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D501" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E501" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="42" customHeight="1">
+      <c r="A502" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C502" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D502" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E502" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="42" customHeight="1">
+      <c r="A503" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C503" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D503" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E503" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="42" customHeight="1">
+      <c r="A504" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C504" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D504" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E504" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="42" customHeight="1">
+      <c r="A505" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B505" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C505" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D505" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E505" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="42" customHeight="1">
+      <c r="A506" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C506" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D506" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E506" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="42" customHeight="1">
+      <c r="A507" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B507" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C507" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D507" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E507" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="42" customHeight="1">
+      <c r="A508" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C508" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D508" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E508" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="42" customHeight="1">
+      <c r="A509" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C509" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D509" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E509" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="42" customHeight="1">
+      <c r="A510" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C510" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D510" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="42" customHeight="1">
+      <c r="A511" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B511" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C511" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D511" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E511" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="42" customHeight="1">
+      <c r="A512" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C512" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D512" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E512" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="42" customHeight="1">
+      <c r="A513" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B513" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C513" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D513" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E513" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="42" customHeight="1">
+      <c r="A514" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C514" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D514" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E514" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="42" customHeight="1">
+      <c r="A515" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C515" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D515" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E515" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="42" customHeight="1">
+      <c r="A516" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C516" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D516" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E516" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="42" customHeight="1">
+      <c r="A517" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C517" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D517" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E517" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="42" customHeight="1">
+      <c r="A518" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C518" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D518" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E518" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="42" customHeight="1">
+      <c r="A519" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B519" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C519" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D519" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E519" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E445"/>
+  <autoFilter ref="A1:E519"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$519</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$594</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E519"/>
+  <dimension ref="A1:E594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12410,8 +12410,1733 @@
         </is>
       </c>
     </row>
+    <row r="520" ht="42" customHeight="1">
+      <c r="A520" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C520" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D520" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E520" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="521" ht="42" customHeight="1">
+      <c r="A521" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B521" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C521" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D521" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E521" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="42" customHeight="1">
+      <c r="A522" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C522" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D522" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E522" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="42" customHeight="1">
+      <c r="A523" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B523" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C523" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D523" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E523" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="42" customHeight="1">
+      <c r="A524" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C524" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D524" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E524" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" ht="42" customHeight="1">
+      <c r="A525" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B525" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C525" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D525" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E525" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="42" customHeight="1">
+      <c r="A526" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B526" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C526" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D526" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E526" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="42" customHeight="1">
+      <c r="A527" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B527" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C527" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D527" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E527" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="42" customHeight="1">
+      <c r="A528" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B528" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C528" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D528" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E528" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="42" customHeight="1">
+      <c r="A529" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B529" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C529" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D529" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E529" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="42" customHeight="1">
+      <c r="A530" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B530" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C530" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D530" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E530" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="42" customHeight="1">
+      <c r="A531" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C531" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D531" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E531" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="42" customHeight="1">
+      <c r="A532" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C532" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D532" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E532" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="42" customHeight="1">
+      <c r="A533" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B533" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C533" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D533" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E533" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="42" customHeight="1">
+      <c r="A534" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B534" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C534" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D534" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E534" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="535" ht="42" customHeight="1">
+      <c r="A535" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C535" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D535" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E535" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="42" customHeight="1">
+      <c r="A536" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C536" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D536" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E536" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="537" ht="42" customHeight="1">
+      <c r="A537" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C537" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D537" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E537" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="42" customHeight="1">
+      <c r="A538" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B538" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C538" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D538" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E538" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="42" customHeight="1">
+      <c r="A539" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B539" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C539" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D539" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E539" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="42" customHeight="1">
+      <c r="A540" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B540" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C540" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D540" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E540" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="42" customHeight="1">
+      <c r="A541" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B541" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C541" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D541" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E541" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="42" customHeight="1">
+      <c r="A542" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B542" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C542" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D542" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E542" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="42" customHeight="1">
+      <c r="A543" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B543" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C543" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D543" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E543" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="42" customHeight="1">
+      <c r="A544" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C544" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D544" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E544" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="42" customHeight="1">
+      <c r="A545" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B545" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C545" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D545" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E545" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="42" customHeight="1">
+      <c r="A546" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B546" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C546" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D546" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E546" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="42" customHeight="1">
+      <c r="A547" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B547" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C547" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D547" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E547" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="42" customHeight="1">
+      <c r="A548" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C548" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D548" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E548" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="42" customHeight="1">
+      <c r="A549" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B549" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C549" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D549" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E549" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="550" ht="42" customHeight="1">
+      <c r="A550" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B550" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C550" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D550" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E550" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="42" customHeight="1">
+      <c r="A551" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B551" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C551" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D551" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E551" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="42" customHeight="1">
+      <c r="A552" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B552" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C552" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D552" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E552" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="42" customHeight="1">
+      <c r="A553" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B553" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C553" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D553" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E553" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="42" customHeight="1">
+      <c r="A554" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B554" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C554" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D554" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E554" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="42" customHeight="1">
+      <c r="A555" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B555" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C555" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D555" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E555" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="42" customHeight="1">
+      <c r="A556" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B556" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C556" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D556" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E556" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="557" ht="42" customHeight="1">
+      <c r="A557" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B557" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C557" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D557" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E557" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="558" ht="42" customHeight="1">
+      <c r="A558" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B558" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C558" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D558" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E558" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="42" customHeight="1">
+      <c r="A559" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B559" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C559" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D559" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E559" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="42" customHeight="1">
+      <c r="A560" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B560" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C560" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D560" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E560" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="561" ht="42" customHeight="1">
+      <c r="A561" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B561" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C561" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D561" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E561" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="42" customHeight="1">
+      <c r="A562" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B562" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C562" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D562" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E562" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="42" customHeight="1">
+      <c r="A563" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B563" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C563" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D563" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E563" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="42" customHeight="1">
+      <c r="A564" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C564" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D564" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E564" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="42" customHeight="1">
+      <c r="A565" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B565" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C565" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D565" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E565" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="42" customHeight="1">
+      <c r="A566" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B566" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C566" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D566" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E566" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="42" customHeight="1">
+      <c r="A567" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C567" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D567" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E567" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="42" customHeight="1">
+      <c r="A568" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B568" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C568" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D568" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E568" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="42" customHeight="1">
+      <c r="A569" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B569" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C569" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D569" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E569" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="42" customHeight="1">
+      <c r="A570" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B570" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C570" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D570" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E570" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="42" customHeight="1">
+      <c r="A571" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B571" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C571" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D571" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E571" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="42" customHeight="1">
+      <c r="A572" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B572" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C572" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D572" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E572" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="42" customHeight="1">
+      <c r="A573" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B573" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C573" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D573" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E573" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="42" customHeight="1">
+      <c r="A574" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B574" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C574" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D574" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E574" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="575" ht="42" customHeight="1">
+      <c r="A575" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B575" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C575" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D575" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E575" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="42" customHeight="1">
+      <c r="A576" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B576" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C576" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D576" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E576" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="42" customHeight="1">
+      <c r="A577" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B577" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C577" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D577" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E577" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="42" customHeight="1">
+      <c r="A578" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B578" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C578" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D578" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E578" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="42" customHeight="1">
+      <c r="A579" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B579" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C579" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D579" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E579" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="42" customHeight="1">
+      <c r="A580" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B580" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C580" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D580" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E580" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="42" customHeight="1">
+      <c r="A581" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B581" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C581" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D581" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E581" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="42" customHeight="1">
+      <c r="A582" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B582" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C582" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D582" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E582" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="42" customHeight="1">
+      <c r="A583" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B583" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C583" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D583" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E583" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="42" customHeight="1">
+      <c r="A584" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B584" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C584" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D584" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E584" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="585" ht="42" customHeight="1">
+      <c r="A585" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B585" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C585" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D585" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E585" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="586" ht="42" customHeight="1">
+      <c r="A586" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B586" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C586" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D586" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E586" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="42" customHeight="1">
+      <c r="A587" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B587" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C587" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D587" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E587" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="588" ht="42" customHeight="1">
+      <c r="A588" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B588" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C588" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D588" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E588" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="589" ht="42" customHeight="1">
+      <c r="A589" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B589" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C589" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D589" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E589" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="590" ht="42" customHeight="1">
+      <c r="A590" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B590" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C590" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D590" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E590" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="591" ht="42" customHeight="1">
+      <c r="A591" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B591" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C591" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D591" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E591" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="42" customHeight="1">
+      <c r="A592" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B592" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C592" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D592" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E592" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="42" customHeight="1">
+      <c r="A593" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B593" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C593" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D593" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E593" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="42" customHeight="1">
+      <c r="A594" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B594" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C594" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D594" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E594" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E519"/>
+  <autoFilter ref="A1:E594"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12422,7 +14147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12541,8 +14266,176 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>% ALTERADA</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>% ALTERADA</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>% ALTERADA</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>% ALTERADA</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$594</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$708</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E594"/>
+  <dimension ref="A1:E708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14135,8 +14135,2630 @@
         </is>
       </c>
     </row>
+    <row r="595" ht="42" customHeight="1">
+      <c r="A595" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B595" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C595" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D595" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E595" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="42" customHeight="1">
+      <c r="A596" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B596" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C596" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D596" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E596" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="42" customHeight="1">
+      <c r="A597" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B597" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C597" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D597" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E597" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="42" customHeight="1">
+      <c r="A598" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B598" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C598" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D598" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E598" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="599" ht="42" customHeight="1">
+      <c r="A599" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B599" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C599" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D599" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E599" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="600" ht="42" customHeight="1">
+      <c r="A600" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B600" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C600" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D600" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E600" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="601" ht="42" customHeight="1">
+      <c r="A601" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B601" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C601" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D601" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E601" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="602" ht="42" customHeight="1">
+      <c r="A602" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B602" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C602" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D602" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E602" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="603" ht="42" customHeight="1">
+      <c r="A603" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B603" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C603" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D603" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E603" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="604" ht="42" customHeight="1">
+      <c r="A604" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B604" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C604" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D604" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E604" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="605" ht="42" customHeight="1">
+      <c r="A605" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B605" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C605" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D605" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E605" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="606" ht="42" customHeight="1">
+      <c r="A606" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B606" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C606" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D606" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E606" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="607" ht="42" customHeight="1">
+      <c r="A607" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B607" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C607" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D607" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E607" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="608" ht="42" customHeight="1">
+      <c r="A608" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B608" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C608" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D608" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E608" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="609" ht="42" customHeight="1">
+      <c r="A609" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B609" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C609" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D609" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E609" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="42" customHeight="1">
+      <c r="A610" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B610" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C610" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D610" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E610" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="42" customHeight="1">
+      <c r="A611" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B611" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C611" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D611" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E611" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="42" customHeight="1">
+      <c r="A612" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B612" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C612" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D612" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E612" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="613" ht="42" customHeight="1">
+      <c r="A613" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B613" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C613" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D613" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E613" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="614" ht="42" customHeight="1">
+      <c r="A614" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B614" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C614" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D614" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E614" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="615" ht="42" customHeight="1">
+      <c r="A615" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B615" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C615" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D615" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E615" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="616" ht="42" customHeight="1">
+      <c r="A616" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B616" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C616" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D616" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E616" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="42" customHeight="1">
+      <c r="A617" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B617" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C617" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D617" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E617" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="618" ht="42" customHeight="1">
+      <c r="A618" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B618" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C618" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D618" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E618" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="42" customHeight="1">
+      <c r="A619" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B619" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C619" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D619" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E619" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="620" ht="42" customHeight="1">
+      <c r="A620" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B620" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C620" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D620" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E620" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="621" ht="42" customHeight="1">
+      <c r="A621" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B621" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C621" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D621" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E621" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="622" ht="42" customHeight="1">
+      <c r="A622" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B622" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C622" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D622" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E622" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="623" ht="42" customHeight="1">
+      <c r="A623" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B623" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C623" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D623" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E623" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="624" ht="42" customHeight="1">
+      <c r="A624" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B624" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C624" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D624" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E624" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="625" ht="42" customHeight="1">
+      <c r="A625" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B625" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C625" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D625" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E625" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="626" ht="42" customHeight="1">
+      <c r="A626" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B626" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C626" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D626" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E626" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="627" ht="42" customHeight="1">
+      <c r="A627" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B627" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C627" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D627" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E627" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="628" ht="42" customHeight="1">
+      <c r="A628" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B628" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C628" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D628" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E628" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="629" ht="42" customHeight="1">
+      <c r="A629" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B629" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C629" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D629" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E629" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="630" ht="42" customHeight="1">
+      <c r="A630" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B630" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C630" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D630" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E630" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="631" ht="42" customHeight="1">
+      <c r="A631" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B631" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C631" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D631" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E631" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="632" ht="42" customHeight="1">
+      <c r="A632" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B632" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C632" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D632" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E632" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="633" ht="42" customHeight="1">
+      <c r="A633" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B633" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C633" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D633" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E633" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="634" ht="42" customHeight="1">
+      <c r="A634" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B634" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C634" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D634" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E634" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="635" ht="42" customHeight="1">
+      <c r="A635" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B635" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C635" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D635" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E635" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="636" ht="42" customHeight="1">
+      <c r="A636" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B636" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C636" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D636" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E636" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="637" ht="42" customHeight="1">
+      <c r="A637" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B637" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C637" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D637" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E637" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="638" ht="42" customHeight="1">
+      <c r="A638" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B638" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C638" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D638" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E638" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="639" ht="42" customHeight="1">
+      <c r="A639" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B639" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C639" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D639" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E639" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="640" ht="42" customHeight="1">
+      <c r="A640" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B640" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C640" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D640" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E640" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="641" ht="42" customHeight="1">
+      <c r="A641" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B641" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C641" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D641" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E641" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="642" ht="42" customHeight="1">
+      <c r="A642" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B642" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C642" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D642" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E642" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="643" ht="42" customHeight="1">
+      <c r="A643" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B643" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C643" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D643" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E643" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="644" ht="42" customHeight="1">
+      <c r="A644" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B644" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C644" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D644" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E644" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="645" ht="42" customHeight="1">
+      <c r="A645" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B645" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C645" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D645" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E645" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="646" ht="42" customHeight="1">
+      <c r="A646" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B646" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C646" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D646" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E646" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="647" ht="42" customHeight="1">
+      <c r="A647" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B647" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C647" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D647" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E647" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="648" ht="42" customHeight="1">
+      <c r="A648" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B648" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C648" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D648" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E648" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="649" ht="42" customHeight="1">
+      <c r="A649" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B649" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C649" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D649" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E649" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="650" ht="42" customHeight="1">
+      <c r="A650" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B650" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C650" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D650" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E650" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="651" ht="42" customHeight="1">
+      <c r="A651" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B651" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C651" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D651" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E651" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="652" ht="42" customHeight="1">
+      <c r="A652" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B652" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C652" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D652" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E652" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="653" ht="42" customHeight="1">
+      <c r="A653" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B653" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C653" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D653" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E653" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="654" ht="42" customHeight="1">
+      <c r="A654" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B654" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C654" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D654" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E654" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="655" ht="42" customHeight="1">
+      <c r="A655" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B655" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C655" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D655" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E655" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="656" ht="42" customHeight="1">
+      <c r="A656" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C656" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D656" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E656" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="657" ht="42" customHeight="1">
+      <c r="A657" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B657" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C657" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D657" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E657" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="658" ht="42" customHeight="1">
+      <c r="A658" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B658" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C658" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D658" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E658" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="659" ht="42" customHeight="1">
+      <c r="A659" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B659" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C659" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D659" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E659" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="660" ht="42" customHeight="1">
+      <c r="A660" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B660" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C660" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D660" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E660" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="661" ht="42" customHeight="1">
+      <c r="A661" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B661" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C661" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D661" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E661" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="662" ht="42" customHeight="1">
+      <c r="A662" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B662" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C662" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D662" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E662" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="663" ht="42" customHeight="1">
+      <c r="A663" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B663" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C663" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D663" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E663" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="664" ht="42" customHeight="1">
+      <c r="A664" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B664" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C664" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D664" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E664" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="665" ht="42" customHeight="1">
+      <c r="A665" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C665" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D665" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E665" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="666" ht="42" customHeight="1">
+      <c r="A666" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B666" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C666" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D666" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E666" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="667" ht="42" customHeight="1">
+      <c r="A667" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B667" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C667" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D667" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E667" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="668" ht="42" customHeight="1">
+      <c r="A668" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B668" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C668" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D668" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E668" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="669" ht="42" customHeight="1">
+      <c r="A669" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B669" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C669" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D669" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E669" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="670" ht="42" customHeight="1">
+      <c r="A670" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B670" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C670" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D670" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E670" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="671" ht="42" customHeight="1">
+      <c r="A671" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B671" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C671" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D671" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E671" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="672" ht="42" customHeight="1">
+      <c r="A672" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B672" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C672" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D672" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E672" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="673" ht="42" customHeight="1">
+      <c r="A673" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B673" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C673" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D673" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E673" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="674" ht="42" customHeight="1">
+      <c r="A674" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B674" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C674" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D674" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E674" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="675" ht="42" customHeight="1">
+      <c r="A675" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B675" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C675" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D675" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E675" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="676" ht="42" customHeight="1">
+      <c r="A676" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B676" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C676" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D676" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E676" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="677" ht="42" customHeight="1">
+      <c r="A677" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B677" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C677" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D677" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E677" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="678" ht="42" customHeight="1">
+      <c r="A678" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B678" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C678" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D678" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E678" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="679" ht="42" customHeight="1">
+      <c r="A679" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B679" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C679" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D679" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E679" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="680" ht="42" customHeight="1">
+      <c r="A680" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B680" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C680" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D680" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E680" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="681" ht="42" customHeight="1">
+      <c r="A681" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B681" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C681" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D681" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E681" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="682" ht="42" customHeight="1">
+      <c r="A682" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B682" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C682" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D682" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E682" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="683" ht="42" customHeight="1">
+      <c r="A683" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B683" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C683" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D683" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E683" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="684" ht="42" customHeight="1">
+      <c r="A684" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B684" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C684" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D684" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E684" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="685" ht="42" customHeight="1">
+      <c r="A685" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B685" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C685" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D685" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E685" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="686" ht="42" customHeight="1">
+      <c r="A686" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B686" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C686" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D686" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E686" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="687" ht="42" customHeight="1">
+      <c r="A687" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B687" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C687" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D687" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E687" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="688" ht="42" customHeight="1">
+      <c r="A688" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B688" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C688" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D688" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E688" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="689" ht="42" customHeight="1">
+      <c r="A689" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B689" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C689" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D689" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E689" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="690" ht="42" customHeight="1">
+      <c r="A690" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B690" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C690" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D690" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E690" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="691" ht="42" customHeight="1">
+      <c r="A691" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B691" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C691" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D691" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E691" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="692" ht="42" customHeight="1">
+      <c r="A692" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B692" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C692" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D692" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E692" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="693" ht="42" customHeight="1">
+      <c r="A693" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B693" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C693" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D693" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E693" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="694" ht="42" customHeight="1">
+      <c r="A694" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B694" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C694" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D694" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E694" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="695" ht="42" customHeight="1">
+      <c r="A695" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B695" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C695" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D695" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E695" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="696" ht="42" customHeight="1">
+      <c r="A696" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B696" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C696" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D696" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E696" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="697" ht="42" customHeight="1">
+      <c r="A697" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B697" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C697" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D697" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E697" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="698" ht="42" customHeight="1">
+      <c r="A698" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B698" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C698" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D698" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E698" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="699" ht="42" customHeight="1">
+      <c r="A699" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B699" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C699" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D699" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E699" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="700" ht="42" customHeight="1">
+      <c r="A700" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B700" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C700" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D700" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E700" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="701" ht="42" customHeight="1">
+      <c r="A701" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B701" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C701" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D701" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E701" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="702" ht="42" customHeight="1">
+      <c r="A702" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B702" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C702" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D702" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E702" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="703" ht="42" customHeight="1">
+      <c r="A703" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B703" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C703" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D703" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E703" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="704" ht="42" customHeight="1">
+      <c r="A704" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B704" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C704" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D704" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E704" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="705" ht="42" customHeight="1">
+      <c r="A705" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B705" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C705" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D705" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E705" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="706" ht="42" customHeight="1">
+      <c r="A706" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B706" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C706" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D706" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E706" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="707" ht="42" customHeight="1">
+      <c r="A707" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B707" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C707" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D707" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E707" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="708" ht="42" customHeight="1">
+      <c r="A708" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B708" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C708" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D708" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E708" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E594"/>
+  <autoFilter ref="A1:E708"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$708</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$746</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E708"/>
+  <dimension ref="A1:E746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16757,8 +16757,882 @@
         </is>
       </c>
     </row>
+    <row r="709" ht="42" customHeight="1">
+      <c r="A709" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B709" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C709" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D709" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E709" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="710" ht="42" customHeight="1">
+      <c r="A710" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B710" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C710" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D710" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E710" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="711" ht="42" customHeight="1">
+      <c r="A711" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B711" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C711" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D711" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E711" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="712" ht="42" customHeight="1">
+      <c r="A712" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B712" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C712" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D712" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E712" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="713" ht="42" customHeight="1">
+      <c r="A713" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B713" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C713" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D713" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E713" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="714" ht="42" customHeight="1">
+      <c r="A714" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B714" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C714" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D714" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E714" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="715" ht="42" customHeight="1">
+      <c r="A715" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B715" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C715" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D715" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E715" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="716" ht="42" customHeight="1">
+      <c r="A716" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B716" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C716" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D716" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E716" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="717" ht="42" customHeight="1">
+      <c r="A717" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B717" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C717" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D717" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E717" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="718" ht="42" customHeight="1">
+      <c r="A718" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B718" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C718" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D718" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E718" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="719" ht="42" customHeight="1">
+      <c r="A719" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B719" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C719" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D719" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E719" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="720" ht="42" customHeight="1">
+      <c r="A720" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B720" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C720" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D720" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E720" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="721" ht="42" customHeight="1">
+      <c r="A721" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B721" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C721" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D721" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E721" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="722" ht="42" customHeight="1">
+      <c r="A722" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B722" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C722" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D722" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E722" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="723" ht="42" customHeight="1">
+      <c r="A723" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B723" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C723" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D723" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E723" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="724" ht="42" customHeight="1">
+      <c r="A724" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B724" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C724" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D724" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E724" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="725" ht="42" customHeight="1">
+      <c r="A725" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B725" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C725" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D725" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E725" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="726" ht="42" customHeight="1">
+      <c r="A726" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B726" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C726" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D726" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E726" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="727" ht="42" customHeight="1">
+      <c r="A727" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B727" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C727" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D727" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E727" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="728" ht="42" customHeight="1">
+      <c r="A728" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B728" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C728" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D728" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E728" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="729" ht="42" customHeight="1">
+      <c r="A729" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B729" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C729" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D729" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E729" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="730" ht="42" customHeight="1">
+      <c r="A730" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B730" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C730" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D730" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E730" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="731" ht="42" customHeight="1">
+      <c r="A731" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B731" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C731" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D731" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E731" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="732" ht="42" customHeight="1">
+      <c r="A732" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B732" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C732" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D732" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E732" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="733" ht="42" customHeight="1">
+      <c r="A733" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B733" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C733" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D733" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E733" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="734" ht="42" customHeight="1">
+      <c r="A734" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B734" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C734" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D734" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E734" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="735" ht="42" customHeight="1">
+      <c r="A735" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B735" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C735" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D735" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E735" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="736" ht="42" customHeight="1">
+      <c r="A736" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B736" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C736" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D736" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E736" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="737" ht="42" customHeight="1">
+      <c r="A737" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B737" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C737" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D737" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E737" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="738" ht="42" customHeight="1">
+      <c r="A738" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B738" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C738" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D738" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E738" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="739" ht="42" customHeight="1">
+      <c r="A739" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B739" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C739" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D739" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E739" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="740" ht="42" customHeight="1">
+      <c r="A740" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B740" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C740" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D740" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E740" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="741" ht="42" customHeight="1">
+      <c r="A741" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B741" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C741" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D741" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E741" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="742" ht="42" customHeight="1">
+      <c r="A742" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B742" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C742" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D742" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E742" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="743" ht="42" customHeight="1">
+      <c r="A743" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B743" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C743" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D743" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E743" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="744" ht="42" customHeight="1">
+      <c r="A744" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B744" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C744" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D744" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E744" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="745" ht="42" customHeight="1">
+      <c r="A745" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B745" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C745" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D745" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E745" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="746" ht="42" customHeight="1">
+      <c r="A746" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B746" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C746" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D746" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E746" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E708"/>
+  <autoFilter ref="A1:E746"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$784</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E746"/>
+  <dimension ref="A1:E784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17631,8 +17631,882 @@
         </is>
       </c>
     </row>
+    <row r="747" ht="42" customHeight="1">
+      <c r="A747" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B747" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C747" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D747" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E747" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="748" ht="42" customHeight="1">
+      <c r="A748" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B748" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C748" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D748" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E748" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="749" ht="42" customHeight="1">
+      <c r="A749" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B749" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C749" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D749" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E749" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="750" ht="42" customHeight="1">
+      <c r="A750" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B750" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C750" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D750" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E750" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="751" ht="42" customHeight="1">
+      <c r="A751" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B751" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C751" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D751" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E751" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="752" ht="42" customHeight="1">
+      <c r="A752" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B752" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C752" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D752" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E752" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="753" ht="42" customHeight="1">
+      <c r="A753" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B753" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C753" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D753" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E753" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="754" ht="42" customHeight="1">
+      <c r="A754" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B754" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C754" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D754" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E754" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="755" ht="42" customHeight="1">
+      <c r="A755" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B755" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C755" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D755" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E755" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="756" ht="42" customHeight="1">
+      <c r="A756" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B756" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C756" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D756" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E756" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="757" ht="42" customHeight="1">
+      <c r="A757" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B757" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C757" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D757" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E757" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="758" ht="42" customHeight="1">
+      <c r="A758" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B758" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C758" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D758" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E758" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="759" ht="42" customHeight="1">
+      <c r="A759" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B759" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C759" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D759" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E759" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="760" ht="42" customHeight="1">
+      <c r="A760" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B760" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C760" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D760" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E760" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="761" ht="42" customHeight="1">
+      <c r="A761" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B761" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C761" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D761" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E761" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="762" ht="42" customHeight="1">
+      <c r="A762" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B762" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C762" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D762" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E762" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="763" ht="42" customHeight="1">
+      <c r="A763" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B763" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C763" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D763" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E763" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="764" ht="42" customHeight="1">
+      <c r="A764" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B764" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C764" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D764" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E764" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="765" ht="42" customHeight="1">
+      <c r="A765" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B765" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C765" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D765" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E765" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="766" ht="42" customHeight="1">
+      <c r="A766" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B766" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C766" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D766" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E766" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="767" ht="42" customHeight="1">
+      <c r="A767" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B767" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C767" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D767" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E767" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="768" ht="42" customHeight="1">
+      <c r="A768" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B768" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C768" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D768" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E768" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="769" ht="42" customHeight="1">
+      <c r="A769" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B769" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C769" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D769" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E769" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="770" ht="42" customHeight="1">
+      <c r="A770" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B770" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C770" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D770" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E770" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="771" ht="42" customHeight="1">
+      <c r="A771" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B771" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C771" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D771" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E771" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="772" ht="42" customHeight="1">
+      <c r="A772" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B772" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C772" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D772" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E772" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="773" ht="42" customHeight="1">
+      <c r="A773" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B773" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C773" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D773" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E773" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="774" ht="42" customHeight="1">
+      <c r="A774" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B774" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C774" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D774" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E774" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="775" ht="42" customHeight="1">
+      <c r="A775" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B775" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C775" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D775" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E775" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="776" ht="42" customHeight="1">
+      <c r="A776" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B776" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C776" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D776" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E776" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="777" ht="42" customHeight="1">
+      <c r="A777" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B777" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C777" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D777" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E777" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="778" ht="42" customHeight="1">
+      <c r="A778" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B778" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C778" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D778" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E778" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="779" ht="42" customHeight="1">
+      <c r="A779" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B779" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C779" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D779" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E779" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="780" ht="42" customHeight="1">
+      <c r="A780" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B780" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C780" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D780" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E780" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="781" ht="42" customHeight="1">
+      <c r="A781" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B781" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C781" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D781" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E781" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="782" ht="42" customHeight="1">
+      <c r="A782" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B782" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C782" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D782" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E782" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="783" ht="42" customHeight="1">
+      <c r="A783" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B783" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C783" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D783" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E783" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="784" ht="42" customHeight="1">
+      <c r="A784" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B784" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C784" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D784" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E784" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E746"/>
+  <autoFilter ref="A1:E784"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$784</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$822</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E784"/>
+  <dimension ref="A1:E822"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18505,8 +18505,882 @@
         </is>
       </c>
     </row>
+    <row r="785" ht="42" customHeight="1">
+      <c r="A785" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B785" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C785" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D785" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E785" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="786" ht="42" customHeight="1">
+      <c r="A786" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B786" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C786" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D786" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E786" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="787" ht="42" customHeight="1">
+      <c r="A787" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B787" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C787" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D787" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E787" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="788" ht="42" customHeight="1">
+      <c r="A788" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B788" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C788" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D788" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E788" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="789" ht="42" customHeight="1">
+      <c r="A789" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B789" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C789" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D789" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E789" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="790" ht="42" customHeight="1">
+      <c r="A790" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B790" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C790" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D790" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E790" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="791" ht="42" customHeight="1">
+      <c r="A791" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B791" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C791" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D791" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E791" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="792" ht="42" customHeight="1">
+      <c r="A792" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B792" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C792" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D792" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E792" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="793" ht="42" customHeight="1">
+      <c r="A793" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B793" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C793" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D793" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E793" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="794" ht="42" customHeight="1">
+      <c r="A794" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B794" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C794" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D794" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E794" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="795" ht="42" customHeight="1">
+      <c r="A795" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B795" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C795" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D795" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E795" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="796" ht="42" customHeight="1">
+      <c r="A796" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B796" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C796" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D796" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E796" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="797" ht="42" customHeight="1">
+      <c r="A797" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B797" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C797" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D797" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E797" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="798" ht="42" customHeight="1">
+      <c r="A798" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B798" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C798" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D798" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E798" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="799" ht="42" customHeight="1">
+      <c r="A799" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B799" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C799" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D799" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E799" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="800" ht="42" customHeight="1">
+      <c r="A800" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B800" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C800" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D800" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E800" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="801" ht="42" customHeight="1">
+      <c r="A801" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B801" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C801" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D801" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E801" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="802" ht="42" customHeight="1">
+      <c r="A802" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B802" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C802" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D802" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E802" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="803" ht="42" customHeight="1">
+      <c r="A803" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B803" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C803" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D803" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E803" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="804" ht="42" customHeight="1">
+      <c r="A804" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B804" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C804" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D804" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E804" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="805" ht="42" customHeight="1">
+      <c r="A805" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B805" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C805" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D805" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E805" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="806" ht="42" customHeight="1">
+      <c r="A806" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B806" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C806" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D806" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E806" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="807" ht="42" customHeight="1">
+      <c r="A807" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B807" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C807" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D807" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E807" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="808" ht="42" customHeight="1">
+      <c r="A808" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B808" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C808" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D808" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E808" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="809" ht="42" customHeight="1">
+      <c r="A809" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B809" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C809" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D809" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E809" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="810" ht="42" customHeight="1">
+      <c r="A810" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C810" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D810" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E810" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="811" ht="42" customHeight="1">
+      <c r="A811" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B811" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C811" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D811" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E811" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="812" ht="42" customHeight="1">
+      <c r="A812" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C812" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D812" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E812" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="813" ht="42" customHeight="1">
+      <c r="A813" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B813" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C813" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D813" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E813" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="814" ht="42" customHeight="1">
+      <c r="A814" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B814" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C814" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D814" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E814" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="815" ht="42" customHeight="1">
+      <c r="A815" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B815" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C815" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D815" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E815" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="816" ht="42" customHeight="1">
+      <c r="A816" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B816" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C816" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D816" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E816" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="817" ht="42" customHeight="1">
+      <c r="A817" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B817" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C817" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D817" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E817" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="818" ht="42" customHeight="1">
+      <c r="A818" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B818" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C818" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D818" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E818" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="819" ht="42" customHeight="1">
+      <c r="A819" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B819" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C819" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D819" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E819" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="820" ht="42" customHeight="1">
+      <c r="A820" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B820" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C820" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D820" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E820" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="821" ht="42" customHeight="1">
+      <c r="A821" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B821" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C821" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D821" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E821" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="822" ht="42" customHeight="1">
+      <c r="A822" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B822" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C822" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D822" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E822" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E784"/>
+  <autoFilter ref="A1:E822"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18517,7 +19391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18804,8 +19678,72 @@
         <v>0.015</v>
       </c>
     </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>REMOVIDO</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H10" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$822</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$860</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E822"/>
+  <dimension ref="A1:E860"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19379,8 +19379,882 @@
         </is>
       </c>
     </row>
+    <row r="823" ht="42" customHeight="1">
+      <c r="A823" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B823" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C823" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D823" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E823" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="824" ht="42" customHeight="1">
+      <c r="A824" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B824" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C824" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D824" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E824" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="825" ht="42" customHeight="1">
+      <c r="A825" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B825" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C825" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D825" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E825" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="826" ht="42" customHeight="1">
+      <c r="A826" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B826" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C826" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D826" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E826" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="827" ht="42" customHeight="1">
+      <c r="A827" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B827" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C827" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D827" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E827" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="828" ht="42" customHeight="1">
+      <c r="A828" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B828" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C828" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D828" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E828" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="829" ht="42" customHeight="1">
+      <c r="A829" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B829" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C829" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D829" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E829" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="830" ht="42" customHeight="1">
+      <c r="A830" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B830" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C830" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D830" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E830" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="831" ht="42" customHeight="1">
+      <c r="A831" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B831" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C831" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D831" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E831" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="832" ht="42" customHeight="1">
+      <c r="A832" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C832" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D832" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E832" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="833" ht="42" customHeight="1">
+      <c r="A833" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B833" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C833" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D833" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E833" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="834" ht="42" customHeight="1">
+      <c r="A834" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C834" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D834" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="835" ht="42" customHeight="1">
+      <c r="A835" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B835" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C835" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D835" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E835" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="836" ht="42" customHeight="1">
+      <c r="A836" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B836" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C836" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D836" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E836" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="837" ht="42" customHeight="1">
+      <c r="A837" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B837" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C837" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D837" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E837" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="838" ht="42" customHeight="1">
+      <c r="A838" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B838" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C838" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D838" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E838" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="839" ht="42" customHeight="1">
+      <c r="A839" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B839" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C839" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D839" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E839" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="840" ht="42" customHeight="1">
+      <c r="A840" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B840" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C840" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D840" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E840" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="841" ht="42" customHeight="1">
+      <c r="A841" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B841" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C841" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D841" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E841" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="842" ht="42" customHeight="1">
+      <c r="A842" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B842" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C842" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D842" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E842" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="843" ht="42" customHeight="1">
+      <c r="A843" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B843" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C843" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D843" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E843" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="844" ht="42" customHeight="1">
+      <c r="A844" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B844" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C844" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D844" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="845" ht="42" customHeight="1">
+      <c r="A845" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B845" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C845" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D845" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E845" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="846" ht="42" customHeight="1">
+      <c r="A846" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B846" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C846" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D846" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E846" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="847" ht="42" customHeight="1">
+      <c r="A847" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B847" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C847" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D847" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E847" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="848" ht="42" customHeight="1">
+      <c r="A848" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B848" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C848" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D848" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="849" ht="42" customHeight="1">
+      <c r="A849" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B849" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C849" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D849" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E849" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="850" ht="42" customHeight="1">
+      <c r="A850" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C850" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D850" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E850" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="851" ht="42" customHeight="1">
+      <c r="A851" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B851" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C851" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D851" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E851" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="852" ht="42" customHeight="1">
+      <c r="A852" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C852" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D852" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E852" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="853" ht="42" customHeight="1">
+      <c r="A853" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B853" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C853" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D853" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E853" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="854" ht="42" customHeight="1">
+      <c r="A854" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B854" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C854" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D854" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E854" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="855" ht="42" customHeight="1">
+      <c r="A855" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B855" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C855" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D855" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E855" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="856" ht="42" customHeight="1">
+      <c r="A856" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B856" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C856" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D856" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E856" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="857" ht="42" customHeight="1">
+      <c r="A857" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B857" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C857" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D857" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E857" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="858" ht="42" customHeight="1">
+      <c r="A858" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C858" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D858" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="859" ht="42" customHeight="1">
+      <c r="A859" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B859" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C859" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D859" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E859" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="860" ht="42" customHeight="1">
+      <c r="A860" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B860" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C860" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D860" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E860" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E822"/>
+  <autoFilter ref="A1:E860"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$860</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$898</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E860"/>
+  <dimension ref="A1:E898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20253,8 +20253,882 @@
         </is>
       </c>
     </row>
+    <row r="861" ht="42" customHeight="1">
+      <c r="A861" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C861" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D861" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E861" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="862" ht="42" customHeight="1">
+      <c r="A862" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B862" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C862" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D862" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="863" ht="42" customHeight="1">
+      <c r="A863" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B863" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C863" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D863" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E863" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="864" ht="42" customHeight="1">
+      <c r="A864" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B864" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C864" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D864" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E864" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="865" ht="42" customHeight="1">
+      <c r="A865" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B865" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C865" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D865" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E865" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="866" ht="42" customHeight="1">
+      <c r="A866" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B866" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C866" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D866" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E866" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="867" ht="42" customHeight="1">
+      <c r="A867" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B867" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C867" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D867" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E867" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="868" ht="42" customHeight="1">
+      <c r="A868" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C868" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D868" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E868" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="869" ht="42" customHeight="1">
+      <c r="A869" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B869" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C869" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D869" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E869" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="870" ht="42" customHeight="1">
+      <c r="A870" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C870" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D870" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E870" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="871" ht="42" customHeight="1">
+      <c r="A871" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B871" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C871" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D871" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E871" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="872" ht="42" customHeight="1">
+      <c r="A872" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C872" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D872" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E872" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="873" ht="42" customHeight="1">
+      <c r="A873" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B873" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C873" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D873" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E873" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="874" ht="42" customHeight="1">
+      <c r="A874" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C874" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D874" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E874" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="875" ht="42" customHeight="1">
+      <c r="A875" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B875" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C875" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D875" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E875" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="876" ht="42" customHeight="1">
+      <c r="A876" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C876" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D876" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E876" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="877" ht="42" customHeight="1">
+      <c r="A877" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B877" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C877" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D877" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E877" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="878" ht="42" customHeight="1">
+      <c r="A878" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C878" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D878" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E878" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="879" ht="42" customHeight="1">
+      <c r="A879" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B879" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C879" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D879" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E879" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="880" ht="42" customHeight="1">
+      <c r="A880" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C880" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D880" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="881" ht="42" customHeight="1">
+      <c r="A881" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B881" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C881" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D881" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E881" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="882" ht="42" customHeight="1">
+      <c r="A882" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C882" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D882" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="883" ht="42" customHeight="1">
+      <c r="A883" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B883" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C883" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D883" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E883" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="884" ht="42" customHeight="1">
+      <c r="A884" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B884" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C884" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D884" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E884" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="885" ht="42" customHeight="1">
+      <c r="A885" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B885" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C885" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D885" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E885" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="886" ht="42" customHeight="1">
+      <c r="A886" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B886" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C886" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D886" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E886" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="887" ht="42" customHeight="1">
+      <c r="A887" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B887" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C887" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D887" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E887" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="888" ht="42" customHeight="1">
+      <c r="A888" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B888" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C888" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D888" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E888" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="889" ht="42" customHeight="1">
+      <c r="A889" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B889" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C889" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D889" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E889" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="890" ht="42" customHeight="1">
+      <c r="A890" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B890" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C890" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D890" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E890" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="891" ht="42" customHeight="1">
+      <c r="A891" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B891" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C891" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D891" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E891" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="892" ht="42" customHeight="1">
+      <c r="A892" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B892" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C892" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D892" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E892" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="893" ht="42" customHeight="1">
+      <c r="A893" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B893" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C893" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D893" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E893" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="894" ht="42" customHeight="1">
+      <c r="A894" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B894" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C894" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D894" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E894" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="895" ht="42" customHeight="1">
+      <c r="A895" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B895" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C895" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D895" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E895" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="896" ht="42" customHeight="1">
+      <c r="A896" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B896" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C896" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D896" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E896" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="897" ht="42" customHeight="1">
+      <c r="A897" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B897" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C897" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D897" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E897" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="898" ht="42" customHeight="1">
+      <c r="A898" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B898" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C898" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D898" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E898" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E860"/>
+  <autoFilter ref="A1:E898"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20265,7 +21139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20616,8 +21490,200 @@
       </c>
       <c r="H10" s="4" t="n"/>
     </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>REMOVIDO</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>REMOVIDO</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>REMOVIDO</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H16" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$898</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$936</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E898"/>
+  <dimension ref="A1:E936"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21127,8 +21127,882 @@
         </is>
       </c>
     </row>
+    <row r="899" ht="42" customHeight="1">
+      <c r="A899" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B899" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C899" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D899" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E899" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="900" ht="42" customHeight="1">
+      <c r="A900" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B900" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C900" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D900" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E900" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="901" ht="42" customHeight="1">
+      <c r="A901" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B901" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C901" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D901" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E901" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="902" ht="42" customHeight="1">
+      <c r="A902" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B902" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C902" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D902" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E902" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="903" ht="42" customHeight="1">
+      <c r="A903" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B903" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C903" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D903" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E903" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="904" ht="42" customHeight="1">
+      <c r="A904" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B904" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C904" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D904" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E904" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="905" ht="42" customHeight="1">
+      <c r="A905" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B905" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C905" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D905" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E905" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="906" ht="42" customHeight="1">
+      <c r="A906" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B906" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C906" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D906" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E906" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="907" ht="42" customHeight="1">
+      <c r="A907" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B907" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C907" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D907" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E907" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="908" ht="42" customHeight="1">
+      <c r="A908" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C908" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D908" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E908" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="909" ht="42" customHeight="1">
+      <c r="A909" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B909" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C909" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D909" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E909" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="910" ht="42" customHeight="1">
+      <c r="A910" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B910" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C910" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D910" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E910" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="911" ht="42" customHeight="1">
+      <c r="A911" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B911" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C911" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D911" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E911" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="912" ht="42" customHeight="1">
+      <c r="A912" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B912" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C912" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D912" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E912" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="913" ht="42" customHeight="1">
+      <c r="A913" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B913" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C913" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D913" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E913" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="914" ht="42" customHeight="1">
+      <c r="A914" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B914" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C914" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D914" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E914" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="915" ht="42" customHeight="1">
+      <c r="A915" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B915" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C915" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D915" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E915" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="916" ht="42" customHeight="1">
+      <c r="A916" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B916" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C916" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D916" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E916" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="917" ht="42" customHeight="1">
+      <c r="A917" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B917" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C917" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D917" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E917" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="918" ht="42" customHeight="1">
+      <c r="A918" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B918" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C918" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D918" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E918" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="919" ht="42" customHeight="1">
+      <c r="A919" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B919" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C919" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D919" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E919" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="920" ht="42" customHeight="1">
+      <c r="A920" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B920" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C920" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D920" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E920" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="921" ht="42" customHeight="1">
+      <c r="A921" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B921" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C921" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D921" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E921" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="922" ht="42" customHeight="1">
+      <c r="A922" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B922" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C922" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D922" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E922" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="923" ht="42" customHeight="1">
+      <c r="A923" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B923" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C923" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D923" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E923" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="924" ht="42" customHeight="1">
+      <c r="A924" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B924" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C924" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D924" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E924" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="925" ht="42" customHeight="1">
+      <c r="A925" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B925" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C925" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D925" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E925" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="926" ht="42" customHeight="1">
+      <c r="A926" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B926" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C926" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D926" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E926" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="927" ht="42" customHeight="1">
+      <c r="A927" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B927" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C927" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D927" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E927" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="928" ht="42" customHeight="1">
+      <c r="A928" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B928" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C928" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D928" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E928" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="929" ht="42" customHeight="1">
+      <c r="A929" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B929" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C929" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D929" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E929" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="930" ht="42" customHeight="1">
+      <c r="A930" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B930" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C930" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D930" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E930" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="931" ht="42" customHeight="1">
+      <c r="A931" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B931" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C931" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D931" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E931" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="932" ht="42" customHeight="1">
+      <c r="A932" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B932" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C932" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D932" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E932" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="933" ht="42" customHeight="1">
+      <c r="A933" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B933" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C933" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D933" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E933" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="934" ht="42" customHeight="1">
+      <c r="A934" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B934" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C934" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D934" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E934" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="935" ht="42" customHeight="1">
+      <c r="A935" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B935" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C935" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D935" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E935" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="936" ht="42" customHeight="1">
+      <c r="A936" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B936" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C936" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D936" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E936" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E898"/>
+  <autoFilter ref="A1:E936"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21139,7 +22013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21682,8 +22556,72 @@
       </c>
       <c r="H16" s="4" t="n"/>
     </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>REMOVIDO</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$936</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$974</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E936"/>
+  <dimension ref="A1:E974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22001,8 +22001,882 @@
         </is>
       </c>
     </row>
+    <row r="937" ht="42" customHeight="1">
+      <c r="A937" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B937" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C937" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D937" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E937" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="938" ht="42" customHeight="1">
+      <c r="A938" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B938" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C938" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D938" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E938" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="939" ht="42" customHeight="1">
+      <c r="A939" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B939" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C939" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D939" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E939" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="940" ht="42" customHeight="1">
+      <c r="A940" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B940" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C940" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D940" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E940" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="941" ht="42" customHeight="1">
+      <c r="A941" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B941" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C941" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D941" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E941" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="942" ht="42" customHeight="1">
+      <c r="A942" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B942" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C942" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D942" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E942" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="943" ht="42" customHeight="1">
+      <c r="A943" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B943" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C943" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D943" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E943" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="944" ht="42" customHeight="1">
+      <c r="A944" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B944" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C944" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D944" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E944" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="945" ht="42" customHeight="1">
+      <c r="A945" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B945" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C945" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D945" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E945" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="946" ht="42" customHeight="1">
+      <c r="A946" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B946" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C946" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D946" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E946" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="947" ht="42" customHeight="1">
+      <c r="A947" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B947" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C947" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D947" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E947" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="948" ht="42" customHeight="1">
+      <c r="A948" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B948" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C948" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D948" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E948" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="949" ht="42" customHeight="1">
+      <c r="A949" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B949" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C949" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D949" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E949" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="950" ht="42" customHeight="1">
+      <c r="A950" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B950" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C950" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D950" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E950" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="951" ht="42" customHeight="1">
+      <c r="A951" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B951" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C951" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D951" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E951" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="952" ht="42" customHeight="1">
+      <c r="A952" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B952" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C952" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D952" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E952" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="953" ht="42" customHeight="1">
+      <c r="A953" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B953" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C953" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D953" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E953" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="954" ht="42" customHeight="1">
+      <c r="A954" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B954" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C954" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D954" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E954" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="955" ht="42" customHeight="1">
+      <c r="A955" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B955" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C955" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D955" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E955" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="956" ht="42" customHeight="1">
+      <c r="A956" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B956" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C956" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D956" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E956" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="957" ht="42" customHeight="1">
+      <c r="A957" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B957" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C957" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D957" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E957" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="958" ht="42" customHeight="1">
+      <c r="A958" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B958" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C958" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D958" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E958" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="959" ht="42" customHeight="1">
+      <c r="A959" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B959" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C959" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D959" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E959" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="960" ht="42" customHeight="1">
+      <c r="A960" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B960" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C960" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D960" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E960" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="961" ht="42" customHeight="1">
+      <c r="A961" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B961" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C961" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D961" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E961" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="962" ht="42" customHeight="1">
+      <c r="A962" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B962" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C962" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D962" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E962" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="963" ht="42" customHeight="1">
+      <c r="A963" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B963" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C963" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D963" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E963" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="964" ht="42" customHeight="1">
+      <c r="A964" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B964" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C964" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D964" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E964" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="965" ht="42" customHeight="1">
+      <c r="A965" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B965" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C965" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D965" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E965" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="966" ht="42" customHeight="1">
+      <c r="A966" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B966" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C966" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D966" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E966" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="967" ht="42" customHeight="1">
+      <c r="A967" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B967" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C967" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D967" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E967" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="968" ht="42" customHeight="1">
+      <c r="A968" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B968" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C968" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D968" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E968" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="969" ht="42" customHeight="1">
+      <c r="A969" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B969" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C969" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D969" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E969" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="970" ht="42" customHeight="1">
+      <c r="A970" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B970" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C970" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D970" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E970" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="971" ht="42" customHeight="1">
+      <c r="A971" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B971" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C971" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D971" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E971" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="972" ht="42" customHeight="1">
+      <c r="A972" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B972" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C972" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D972" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E972" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="973" ht="42" customHeight="1">
+      <c r="A973" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B973" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C973" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D973" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E973" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="974" ht="42" customHeight="1">
+      <c r="A974" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B974" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C974" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D974" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E974" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E936"/>
+  <autoFilter ref="A1:E974"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$974</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1012</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E974"/>
+  <dimension ref="A1:E1012"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22875,8 +22875,882 @@
         </is>
       </c>
     </row>
+    <row r="975" ht="42" customHeight="1">
+      <c r="A975" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B975" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C975" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D975" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E975" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="976" ht="42" customHeight="1">
+      <c r="A976" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B976" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C976" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D976" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E976" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="977" ht="42" customHeight="1">
+      <c r="A977" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B977" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C977" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D977" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E977" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="978" ht="42" customHeight="1">
+      <c r="A978" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B978" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C978" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D978" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E978" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="979" ht="42" customHeight="1">
+      <c r="A979" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B979" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C979" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D979" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E979" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="980" ht="42" customHeight="1">
+      <c r="A980" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B980" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C980" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D980" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E980" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="981" ht="42" customHeight="1">
+      <c r="A981" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B981" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C981" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D981" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E981" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="982" ht="42" customHeight="1">
+      <c r="A982" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B982" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C982" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D982" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E982" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="983" ht="42" customHeight="1">
+      <c r="A983" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B983" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C983" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D983" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E983" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="984" ht="42" customHeight="1">
+      <c r="A984" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B984" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C984" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D984" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E984" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="985" ht="42" customHeight="1">
+      <c r="A985" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B985" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C985" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D985" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E985" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="986" ht="42" customHeight="1">
+      <c r="A986" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B986" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C986" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D986" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E986" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="987" ht="42" customHeight="1">
+      <c r="A987" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B987" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C987" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D987" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E987" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="988" ht="42" customHeight="1">
+      <c r="A988" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B988" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C988" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D988" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E988" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="989" ht="42" customHeight="1">
+      <c r="A989" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B989" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C989" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D989" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E989" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="990" ht="42" customHeight="1">
+      <c r="A990" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B990" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C990" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D990" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E990" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="991" ht="42" customHeight="1">
+      <c r="A991" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B991" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C991" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D991" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E991" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="992" ht="42" customHeight="1">
+      <c r="A992" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B992" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C992" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D992" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E992" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="993" ht="42" customHeight="1">
+      <c r="A993" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B993" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C993" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D993" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E993" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="994" ht="42" customHeight="1">
+      <c r="A994" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B994" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C994" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D994" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E994" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="995" ht="42" customHeight="1">
+      <c r="A995" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B995" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C995" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D995" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E995" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="996" ht="42" customHeight="1">
+      <c r="A996" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B996" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C996" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D996" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E996" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="997" ht="42" customHeight="1">
+      <c r="A997" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B997" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C997" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D997" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E997" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="998" ht="42" customHeight="1">
+      <c r="A998" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B998" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C998" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D998" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E998" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="999" ht="42" customHeight="1">
+      <c r="A999" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B999" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C999" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D999" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E999" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000" ht="42" customHeight="1">
+      <c r="A1000" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1000" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1000" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1000" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E1000" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001" ht="42" customHeight="1">
+      <c r="A1001" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1001" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1001" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1001" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E1001" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002" ht="42" customHeight="1">
+      <c r="A1002" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1002" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1002" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1002" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E1002" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003" ht="42" customHeight="1">
+      <c r="A1003" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1003" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1003" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1003" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E1003" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004" ht="42" customHeight="1">
+      <c r="A1004" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1004" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1004" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1004" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E1004" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005" ht="42" customHeight="1">
+      <c r="A1005" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1005" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1005" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1005" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E1005" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006" ht="42" customHeight="1">
+      <c r="A1006" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1006" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1006" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1006" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E1006" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007" ht="42" customHeight="1">
+      <c r="A1007" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1007" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1007" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1007" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E1007" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008" ht="42" customHeight="1">
+      <c r="A1008" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1008" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1008" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1008" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E1008" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009" ht="42" customHeight="1">
+      <c r="A1009" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1009" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1009" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D1009" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E1009" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010" ht="42" customHeight="1">
+      <c r="A1010" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1010" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1010" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1010" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E1010" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011" ht="42" customHeight="1">
+      <c r="A1011" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1011" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1011" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1011" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E1011" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012" ht="42" customHeight="1">
+      <c r="A1012" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1012" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1012" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1012" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E1012" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E974"/>
+  <autoFilter ref="A1:E1012"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1012</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1050</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1012"/>
+  <dimension ref="A1:E1050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23749,8 +23749,882 @@
         </is>
       </c>
     </row>
+    <row r="1013" ht="42" customHeight="1">
+      <c r="A1013" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1013" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1013" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1013" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E1013" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014" ht="42" customHeight="1">
+      <c r="A1014" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1014" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1014" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1014" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E1014" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015" ht="42" customHeight="1">
+      <c r="A1015" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1015" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1015" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1015" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E1015" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016" ht="42" customHeight="1">
+      <c r="A1016" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1016" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1016" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1016" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E1016" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017" ht="42" customHeight="1">
+      <c r="A1017" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1017" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1017" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1017" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E1017" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018" ht="42" customHeight="1">
+      <c r="A1018" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1018" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1018" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1018" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E1018" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019" ht="42" customHeight="1">
+      <c r="A1019" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1019" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1019" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1019" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E1019" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020" ht="42" customHeight="1">
+      <c r="A1020" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1020" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1020" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1020" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E1020" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021" ht="42" customHeight="1">
+      <c r="A1021" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1021" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1021" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D1021" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E1021" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022" ht="42" customHeight="1">
+      <c r="A1022" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1022" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1022" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D1022" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E1022" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023" ht="42" customHeight="1">
+      <c r="A1023" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1023" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1023" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1023" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E1023" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024" ht="42" customHeight="1">
+      <c r="A1024" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1024" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1024" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1024" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E1024" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025" ht="42" customHeight="1">
+      <c r="A1025" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1025" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1025" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1025" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E1025" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026" ht="42" customHeight="1">
+      <c r="A1026" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1026" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1026" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D1026" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E1026" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027" ht="42" customHeight="1">
+      <c r="A1027" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1027" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1027" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1027" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E1027" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028" ht="42" customHeight="1">
+      <c r="A1028" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1028" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1028" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1028" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E1028" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029" ht="42" customHeight="1">
+      <c r="A1029" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1029" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1029" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D1029" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E1029" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030" ht="42" customHeight="1">
+      <c r="A1030" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1030" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1030" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1030" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E1030" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031" ht="42" customHeight="1">
+      <c r="A1031" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1031" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1031" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1031" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E1031" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032" ht="42" customHeight="1">
+      <c r="A1032" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1032" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1032" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D1032" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E1032" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033" ht="42" customHeight="1">
+      <c r="A1033" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1033" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1033" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1033" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E1033" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034" ht="42" customHeight="1">
+      <c r="A1034" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1034" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1034" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D1034" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E1034" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035" ht="42" customHeight="1">
+      <c r="A1035" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1035" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1035" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1035" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E1035" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036" ht="42" customHeight="1">
+      <c r="A1036" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1036" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1036" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1036" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E1036" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037" ht="42" customHeight="1">
+      <c r="A1037" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1037" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1037" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D1037" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E1037" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038" ht="42" customHeight="1">
+      <c r="A1038" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1038" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1038" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1038" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E1038" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039" ht="42" customHeight="1">
+      <c r="A1039" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1039" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1039" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1039" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E1039" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040" ht="42" customHeight="1">
+      <c r="A1040" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1040" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1040" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1040" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E1040" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041" ht="42" customHeight="1">
+      <c r="A1041" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1041" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1041" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1041" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E1041" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042" ht="42" customHeight="1">
+      <c r="A1042" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1042" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1042" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1042" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E1042" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043" ht="42" customHeight="1">
+      <c r="A1043" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1043" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1043" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1043" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E1043" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044" ht="42" customHeight="1">
+      <c r="A1044" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1044" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1044" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1044" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E1044" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045" ht="42" customHeight="1">
+      <c r="A1045" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1045" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1045" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1045" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E1045" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046" ht="42" customHeight="1">
+      <c r="A1046" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1046" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1046" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1046" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E1046" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047" ht="42" customHeight="1">
+      <c r="A1047" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1047" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1047" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D1047" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E1047" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048" ht="42" customHeight="1">
+      <c r="A1048" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1048" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1048" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1048" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E1048" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049" ht="42" customHeight="1">
+      <c r="A1049" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1049" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1049" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1049" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E1049" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050" ht="42" customHeight="1">
+      <c r="A1050" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1050" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1050" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1050" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E1050" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1012"/>
+  <autoFilter ref="A1:E1050"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23761,7 +24635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24368,8 +25242,136 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>REMOVIDO</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>REMOVIDO</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1050</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1088</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1050"/>
+  <dimension ref="A1:E1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24623,8 +24623,882 @@
         </is>
       </c>
     </row>
+    <row r="1051" ht="42" customHeight="1">
+      <c r="A1051" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1051" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1051" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1051" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E1051" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052" ht="42" customHeight="1">
+      <c r="A1052" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1052" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1052" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1052" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E1052" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053" ht="42" customHeight="1">
+      <c r="A1053" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1053" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1053" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1053" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E1053" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054" ht="42" customHeight="1">
+      <c r="A1054" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1054" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1054" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1054" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E1054" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055" ht="42" customHeight="1">
+      <c r="A1055" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1055" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1055" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1055" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E1055" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056" ht="42" customHeight="1">
+      <c r="A1056" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1056" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1056" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1056" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E1056" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057" ht="42" customHeight="1">
+      <c r="A1057" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1057" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1057" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1057" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E1057" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058" ht="42" customHeight="1">
+      <c r="A1058" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1058" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1058" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1058" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E1058" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059" ht="42" customHeight="1">
+      <c r="A1059" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1059" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1059" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D1059" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E1059" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060" ht="42" customHeight="1">
+      <c r="A1060" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1060" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1060" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D1060" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E1060" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061" ht="42" customHeight="1">
+      <c r="A1061" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1061" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1061" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1061" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E1061" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062" ht="42" customHeight="1">
+      <c r="A1062" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1062" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1062" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1062" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E1062" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063" ht="42" customHeight="1">
+      <c r="A1063" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1063" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1063" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1063" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E1063" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064" ht="42" customHeight="1">
+      <c r="A1064" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1064" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1064" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D1064" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E1064" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065" ht="42" customHeight="1">
+      <c r="A1065" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1065" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1065" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1065" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E1065" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066" ht="42" customHeight="1">
+      <c r="A1066" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1066" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1066" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1066" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E1066" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067" ht="42" customHeight="1">
+      <c r="A1067" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1067" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1067" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D1067" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E1067" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068" ht="42" customHeight="1">
+      <c r="A1068" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1068" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1068" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1068" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E1068" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069" ht="42" customHeight="1">
+      <c r="A1069" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1069" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1069" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1069" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E1069" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070" ht="42" customHeight="1">
+      <c r="A1070" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1070" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1070" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D1070" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E1070" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071" ht="42" customHeight="1">
+      <c r="A1071" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1071" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1071" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1071" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E1071" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072" ht="42" customHeight="1">
+      <c r="A1072" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1072" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1072" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D1072" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E1072" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073" ht="42" customHeight="1">
+      <c r="A1073" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1073" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1073" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1073" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E1073" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074" ht="42" customHeight="1">
+      <c r="A1074" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1074" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1074" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1074" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E1074" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075" ht="42" customHeight="1">
+      <c r="A1075" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1075" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1075" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D1075" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E1075" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076" ht="42" customHeight="1">
+      <c r="A1076" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1076" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1076" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1076" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E1076" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077" ht="42" customHeight="1">
+      <c r="A1077" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1077" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1077" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1077" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E1077" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078" ht="42" customHeight="1">
+      <c r="A1078" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1078" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1078" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1078" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E1078" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079" ht="42" customHeight="1">
+      <c r="A1079" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1079" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1079" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1079" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E1079" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080" ht="42" customHeight="1">
+      <c r="A1080" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1080" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1080" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1080" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E1080" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081" ht="42" customHeight="1">
+      <c r="A1081" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1081" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1081" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1081" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E1081" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082" ht="42" customHeight="1">
+      <c r="A1082" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1082" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1082" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1082" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E1082" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083" ht="42" customHeight="1">
+      <c r="A1083" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1083" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1083" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1083" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E1083" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084" ht="42" customHeight="1">
+      <c r="A1084" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1084" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1084" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1084" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E1084" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085" ht="42" customHeight="1">
+      <c r="A1085" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1085" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1085" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D1085" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E1085" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086" ht="42" customHeight="1">
+      <c r="A1086" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1086" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1086" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1086" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E1086" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087" ht="42" customHeight="1">
+      <c r="A1087" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1087" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1087" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1087" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E1087" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088" ht="42" customHeight="1">
+      <c r="A1088" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1088" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1088" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1088" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E1088" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1050"/>
+  <autoFilter ref="A1:E1088"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1088</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1088"/>
+  <dimension ref="A1:E1126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25497,8 +25497,882 @@
         </is>
       </c>
     </row>
+    <row r="1089" ht="42" customHeight="1">
+      <c r="A1089" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1089" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1089" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1089" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E1089" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090" ht="42" customHeight="1">
+      <c r="A1090" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1090" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1090" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1090" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E1090" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091" ht="42" customHeight="1">
+      <c r="A1091" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1091" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1091" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1091" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E1091" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092" ht="42" customHeight="1">
+      <c r="A1092" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1092" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1092" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1092" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E1092" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093" ht="42" customHeight="1">
+      <c r="A1093" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1093" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1093" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1093" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E1093" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094" ht="42" customHeight="1">
+      <c r="A1094" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1094" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1094" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1094" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E1094" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095" ht="42" customHeight="1">
+      <c r="A1095" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1095" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1095" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1095" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E1095" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096" ht="42" customHeight="1">
+      <c r="A1096" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1096" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1096" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1096" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E1096" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097" ht="42" customHeight="1">
+      <c r="A1097" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1097" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1097" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D1097" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E1097" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098" ht="42" customHeight="1">
+      <c r="A1098" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1098" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1098" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D1098" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E1098" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099" ht="42" customHeight="1">
+      <c r="A1099" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1099" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1099" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1099" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E1099" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100" ht="42" customHeight="1">
+      <c r="A1100" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1100" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1100" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1100" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E1100" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101" ht="42" customHeight="1">
+      <c r="A1101" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1101" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1101" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1101" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E1101" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102" ht="42" customHeight="1">
+      <c r="A1102" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1102" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1102" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D1102" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E1102" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103" ht="42" customHeight="1">
+      <c r="A1103" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1103" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1103" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1103" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E1103" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104" ht="42" customHeight="1">
+      <c r="A1104" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1104" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1104" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1104" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E1104" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105" ht="42" customHeight="1">
+      <c r="A1105" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1105" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1105" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D1105" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E1105" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106" ht="42" customHeight="1">
+      <c r="A1106" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1106" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1106" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1106" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E1106" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107" ht="42" customHeight="1">
+      <c r="A1107" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1107" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1107" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1107" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E1107" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108" ht="42" customHeight="1">
+      <c r="A1108" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1108" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1108" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D1108" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E1108" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109" ht="42" customHeight="1">
+      <c r="A1109" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1109" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1109" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1109" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E1109" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110" ht="42" customHeight="1">
+      <c r="A1110" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1110" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1110" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D1110" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E1110" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111" ht="42" customHeight="1">
+      <c r="A1111" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1111" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1111" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1111" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E1111" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112" ht="42" customHeight="1">
+      <c r="A1112" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1112" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1112" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1112" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E1112" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113" ht="42" customHeight="1">
+      <c r="A1113" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1113" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1113" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D1113" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E1113" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114" ht="42" customHeight="1">
+      <c r="A1114" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1114" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1114" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1114" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E1114" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115" ht="42" customHeight="1">
+      <c r="A1115" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1115" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1115" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1115" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E1115" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116" ht="42" customHeight="1">
+      <c r="A1116" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1116" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1116" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1116" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E1116" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117" ht="42" customHeight="1">
+      <c r="A1117" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1117" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1117" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1117" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E1117" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118" ht="42" customHeight="1">
+      <c r="A1118" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1118" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1118" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1118" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E1118" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119" ht="42" customHeight="1">
+      <c r="A1119" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1119" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1119" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1119" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E1119" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120" ht="42" customHeight="1">
+      <c r="A1120" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1120" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1120" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1120" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E1120" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121" ht="42" customHeight="1">
+      <c r="A1121" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1121" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1121" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1121" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E1121" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122" ht="42" customHeight="1">
+      <c r="A1122" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1122" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1122" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1122" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E1122" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123" ht="42" customHeight="1">
+      <c r="A1123" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1123" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1123" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D1123" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E1123" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124" ht="42" customHeight="1">
+      <c r="A1124" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1124" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1124" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1124" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E1124" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125" ht="42" customHeight="1">
+      <c r="A1125" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1125" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1125" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1125" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E1125" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126" ht="42" customHeight="1">
+      <c r="A1126" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1126" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1126" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1126" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E1126" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1088"/>
+  <autoFilter ref="A1:E1126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$1164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1126"/>
+  <dimension ref="A1:E1164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -26371,8 +26371,882 @@
         </is>
       </c>
     </row>
+    <row r="1127" ht="42" customHeight="1">
+      <c r="A1127" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1127" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1127" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1127" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E1127" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128" ht="42" customHeight="1">
+      <c r="A1128" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1128" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1128" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1128" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E1128" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129" ht="42" customHeight="1">
+      <c r="A1129" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1129" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1129" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1129" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E1129" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130" ht="42" customHeight="1">
+      <c r="A1130" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1130" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1130" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1130" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E1130" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131" ht="42" customHeight="1">
+      <c r="A1131" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1131" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1131" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1131" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E1131" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132" ht="42" customHeight="1">
+      <c r="A1132" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1132" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1132" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1132" s="3" t="inlineStr">
+        <is>
+          <t>VALE S.A</t>
+        </is>
+      </c>
+      <c r="E1132" s="3" t="inlineStr">
+        <is>
+          <t>VALE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133" ht="42" customHeight="1">
+      <c r="A1133" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1133" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1133" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1133" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E1133" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134" ht="42" customHeight="1">
+      <c r="A1134" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1134" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C1134" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1134" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E1134" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135" ht="42" customHeight="1">
+      <c r="A1135" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1135" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1135" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D1135" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E1135" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136" ht="42" customHeight="1">
+      <c r="A1136" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1136" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1136" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D1136" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E1136" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137" ht="42" customHeight="1">
+      <c r="A1137" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1137" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1137" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1137" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E1137" s="3" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138" ht="42" customHeight="1">
+      <c r="A1138" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1138" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1138" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1138" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E1138" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139" ht="42" customHeight="1">
+      <c r="A1139" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1139" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1139" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1139" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E1139" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140" ht="42" customHeight="1">
+      <c r="A1140" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1140" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1140" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D1140" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E1140" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141" ht="42" customHeight="1">
+      <c r="A1141" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1141" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1141" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1141" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E1141" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142" ht="42" customHeight="1">
+      <c r="A1142" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1142" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1142" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1142" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E1142" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143" ht="42" customHeight="1">
+      <c r="A1143" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1143" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1143" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D1143" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E1143" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144" ht="42" customHeight="1">
+      <c r="A1144" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1144" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1144" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D1144" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E1144" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145" ht="42" customHeight="1">
+      <c r="A1145" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1145" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C1145" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1145" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E1145" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146" ht="42" customHeight="1">
+      <c r="A1146" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1146" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1146" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D1146" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E1146" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147" ht="42" customHeight="1">
+      <c r="A1147" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1147" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1147" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1147" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E1147" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148" ht="42" customHeight="1">
+      <c r="A1148" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1148" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1148" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D1148" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E1148" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149" ht="42" customHeight="1">
+      <c r="A1149" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1149" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1149" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1149" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E1149" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150" ht="42" customHeight="1">
+      <c r="A1150" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1150" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1150" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1150" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E1150" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151" ht="42" customHeight="1">
+      <c r="A1151" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1151" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C1151" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D1151" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E1151" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152" ht="42" customHeight="1">
+      <c r="A1152" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1152" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1152" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1152" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E1152" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153" ht="42" customHeight="1">
+      <c r="A1153" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1153" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1153" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1153" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E1153" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154" ht="42" customHeight="1">
+      <c r="A1154" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1154" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1154" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1154" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E1154" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155" ht="42" customHeight="1">
+      <c r="A1155" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1155" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1155" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1155" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E1155" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156" ht="42" customHeight="1">
+      <c r="A1156" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1156" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1156" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D1156" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E1156" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157" ht="42" customHeight="1">
+      <c r="A1157" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1157" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1157" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1157" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E1157" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158" ht="42" customHeight="1">
+      <c r="A1158" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1158" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1158" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1158" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E1158" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159" ht="42" customHeight="1">
+      <c r="A1159" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1159" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1159" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D1159" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E1159" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160" ht="42" customHeight="1">
+      <c r="A1160" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1160" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1160" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D1160" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E1160" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161" ht="42" customHeight="1">
+      <c r="A1161" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1161" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1161" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D1161" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E1161" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162" ht="42" customHeight="1">
+      <c r="A1162" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1162" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1162" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1162" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E1162" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163" ht="42" customHeight="1">
+      <c r="A1163" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1163" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1163" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1163" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E1163" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164" ht="42" customHeight="1">
+      <c r="A1164" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1164" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C1164" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D1164" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E1164" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1126"/>
+  <autoFilter ref="A1:E1164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
